--- a/gaming_forms/024_villain_character_profile--gaming_forms.xlsx
+++ b/gaming_forms/024_villain_character_profile--gaming_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'financial',_'label':_'financial_gain'}</t>
+          <t>financial_gain</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'financial', 'label': 'Financial Gain'}</t>
+          <t>Financial Gain</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'power',_'label':_'power'}</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Power', 'label': 'Power'}</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'revenge',_'label':_'revenge'}</t>
+          <t>revenge</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Revenge', 'label': 'Revenge'}</t>
+          <t>Revenge</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'control',_'label':_'control'}</t>
+          <t>control</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Control', 'label': 'Control'}</t>
+          <t>Control</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'mutilation',_'label':_'mutilation'}</t>
+          <t>mutilation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Mutilation', 'label': 'Mutilation'}</t>
+          <t>Mutilation</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'physical',_'label':_'physical'}</t>
+          <t>physical</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Physical', 'label': 'Physical'}</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'psychological',_'label':_'psychological'}</t>
+          <t>psychological</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Psychological', 'label': 'Psychological'}</t>
+          <t>Psychological</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'magical',_'label':_'magical'}</t>
+          <t>magical</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Magical', 'label': 'Magical'}</t>
+          <t>Magical</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'social',_'label':_'social'}</t>
+          <t>social</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Social', 'label': 'Social'}</t>
+          <t>Social</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'cyber',_'label':_'cyber'}</t>
+          <t>cyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Cyber', 'label': 'Cyber'}</t>
+          <t>Cyber</t>
         </is>
       </c>
     </row>
